--- a/releases/BOM_SmartKnob_View.xlsx
+++ b/releases/BOM_SmartKnob_View.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Q2, Q2</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
